--- a/logs/encoders/best_results.xlsx
+++ b/logs/encoders/best_results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="multi_class_ParlVotePlus" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="binary_ConVote" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="multi_class_MotionPolicy" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ner_nerex" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="binary_ParlVote" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ner_ElecDeb60to20" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ner_ArgUNSC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="multi_class_ElecDeb60to20" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="binary_AusHansard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="multi_class_ArgUNSC" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="binary_HanDeSet" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi_class_ParlVotePlus" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="binary_ConVote" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi_class_MotionPolicy" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ner_nerex" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="binary_ParlVote" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ner_ElecDeb60to20" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ner_ArgUNSC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi_class_ElecDeb60to20" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="binary_AusHansard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi_class_ArgUNSC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="binary_HanDeSet" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,21 +52,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,66 +423,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -738,21 +726,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>5e-05</v>
@@ -764,16 +752,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6366429649879222</v>
+        <v>0.6551323184095549</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6289021744157345</v>
+        <v>0.6740048850414965</v>
       </c>
       <c r="K7" t="n">
-        <v>0.655468180582409</v>
+        <v>0.6435763768444689</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6511427339370418</v>
+        <v>0.6774471755066839</v>
       </c>
     </row>
     <row r="8">
@@ -784,17 +772,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -810,16 +798,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.605729002653374</v>
+        <v>0.6366429649879222</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6020543615306304</v>
+        <v>0.6289021744157345</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6254756396315163</v>
+        <v>0.655468180582409</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6269943941354031</v>
+        <v>0.6511427339370418</v>
       </c>
     </row>
     <row r="9">
@@ -830,7 +818,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -840,7 +828,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -856,16 +844,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5622471320695576</v>
+        <v>0.605729002653374</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5524602146219695</v>
+        <v>0.6020543615306304</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5872398116363503</v>
+        <v>0.6254756396315163</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5610176800344976</v>
+        <v>0.6269943941354031</v>
       </c>
     </row>
     <row r="10">
@@ -876,24 +864,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
@@ -902,16 +890,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6019257476788826</v>
+        <v>0.5622471320695576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5845956835229789</v>
+        <v>0.5524602146219695</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6314118142374329</v>
+        <v>0.5872398116363503</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6093143596377749</v>
+        <v>0.5610176800344976</v>
       </c>
     </row>
     <row r="11">
@@ -922,24 +910,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -948,16 +936,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.615202141029628</v>
+        <v>0.6019257476788826</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6065731961977764</v>
+        <v>0.5845956835229789</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6385201364274612</v>
+        <v>0.6314118142374329</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6269943941354031</v>
+        <v>0.6093143596377749</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +956,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -991,18 +979,64 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.615202141029628</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6065731961977764</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6385201364274612</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6269943941354031</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ParlVotePlus</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
         <v>16</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.5605635830057274</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.5409538629798983</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.5991212059138304</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.5623113410952997</v>
       </c>
     </row>
@@ -1017,66 +1051,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -1320,17 +1354,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>ModernBERT-base-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1343,19 +1377,19 @@
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6992540673408048</v>
+        <v>0.7248866732992733</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7000680580762251</v>
+        <v>0.7548958433023895</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7007912769587544</v>
+        <v>0.7013857948093234</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7973713033953997</v>
+        <v>0.8138006571741512</v>
       </c>
     </row>
     <row r="8">
@@ -1366,42 +1400,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7377515144696555</v>
+        <v>0.6992540673408048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7279519463985483</v>
+        <v>0.7000680580762251</v>
       </c>
       <c r="K8" t="n">
-        <v>0.750050733705162</v>
+        <v>0.7007912769587544</v>
       </c>
       <c r="L8" t="n">
-        <v>0.828039430449069</v>
+        <v>0.7973713033953997</v>
       </c>
     </row>
     <row r="9">
@@ -1412,7 +1446,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1422,7 +1456,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1435,19 +1469,19 @@
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6096839627754294</v>
+        <v>0.7377515144696555</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5986119567289657</v>
+        <v>0.7279519463985483</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6324078271668098</v>
+        <v>0.750050733705162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6889375684556407</v>
+        <v>0.828039430449069</v>
       </c>
     </row>
     <row r="10">
@@ -1458,24 +1492,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>bert-base-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
@@ -1484,16 +1518,16 @@
         <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7280923536795578</v>
+        <v>0.6096839627754294</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7109206191774998</v>
+        <v>0.5986119567289657</v>
       </c>
       <c r="K10" t="n">
-        <v>0.753583033428138</v>
+        <v>0.6324078271668098</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7776560788608982</v>
+        <v>0.6889375684556407</v>
       </c>
     </row>
     <row r="11">
@@ -1504,42 +1538,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7126718452497252</v>
+        <v>0.7280923536795578</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7013451199956832</v>
+        <v>0.7109206191774998</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7299249894457659</v>
+        <v>0.753583033428138</v>
       </c>
       <c r="L11" t="n">
-        <v>0.787513691128149</v>
+        <v>0.7776560788608982</v>
       </c>
     </row>
     <row r="12">
@@ -1550,24 +1584,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
@@ -1576,15 +1610,61 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
+        <v>0.7126718452497252</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7013451199956832</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7299249894457659</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.787513691128149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ArgUNSC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.6377004432695424</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.6296793169103069</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.648109462457805</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.7437020810514786</v>
       </c>
     </row>
@@ -1599,66 +1679,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -1902,24 +1982,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
@@ -1928,16 +2008,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7669172932330827</v>
+        <v>0.75177304964539</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7162162162162162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7611940298507462</v>
+        <v>0.7910447761194029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.75</v>
+        <v>0.717741935483871</v>
       </c>
     </row>
     <row r="8">
@@ -1948,17 +2028,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1974,16 +2054,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7518796992481203</v>
+        <v>0.7669172932330827</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="K8" t="n">
-        <v>0.746268656716418</v>
+        <v>0.7611940298507462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7338709677419355</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -1994,7 +2074,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2004,32 +2084,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.765625</v>
+        <v>0.7518796992481203</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7313432835820896</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.7338709677419355</v>
       </c>
     </row>
     <row r="10">
@@ -2040,17 +2120,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2063,19 +2143,19 @@
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.765625</v>
       </c>
       <c r="J10" t="n">
-        <v>0.675</v>
+        <v>0.8032786885245902</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8059701492537313</v>
+        <v>0.7313432835820896</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6854838709677419</v>
+        <v>0.7580645161290323</v>
       </c>
     </row>
     <row r="11">
@@ -2086,42 +2166,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7397260273972602</v>
+        <v>0.675</v>
       </c>
       <c r="K11" t="n">
         <v>0.8059701492537313</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.6854838709677419</v>
       </c>
     </row>
     <row r="12">
@@ -2132,21 +2212,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>3e-05</v>
@@ -2155,18 +2235,64 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7397260273972602</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8059701492537313</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>binary_classification_HanDeSet</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
         <v>32</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.7549668874172185</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.6785714285714286</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.8507462686567164</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.7016129032258065</v>
       </c>
     </row>
@@ -2181,66 +2307,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -2484,21 +2610,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>5e-05</v>
@@ -2510,16 +2636,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8162393162393162</v>
+        <v>0.8268041237113402</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7876288659793814</v>
+        <v>0.7726396917148363</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8470066518847007</v>
+        <v>0.8891352549889135</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7786357786357786</v>
+        <v>0.7837837837837838</v>
       </c>
     </row>
     <row r="8">
@@ -2530,42 +2656,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7986870897155361</v>
+        <v>0.8162393162393162</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7883369330453563</v>
+        <v>0.7876288659793814</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8093126385809313</v>
+        <v>0.8470066518847007</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7631917631917632</v>
+        <v>0.7786357786357786</v>
       </c>
     </row>
     <row r="9">
@@ -2576,7 +2702,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2586,11 +2712,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>3e-05</v>
@@ -2602,16 +2728,16 @@
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7694038245219348</v>
+        <v>0.7986870897155361</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7808219178082192</v>
+        <v>0.7883369330453563</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7583148558758315</v>
+        <v>0.8093126385809313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7361647361647362</v>
+        <v>0.7631917631917632</v>
       </c>
     </row>
     <row r="10">
@@ -2622,24 +2748,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
@@ -2648,16 +2774,16 @@
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8081023454157783</v>
+        <v>0.7694038245219348</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7782340862422998</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8403547671840355</v>
+        <v>0.7583148558758315</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7683397683397684</v>
+        <v>0.7361647361647362</v>
       </c>
     </row>
     <row r="11">
@@ -2668,24 +2794,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -2694,16 +2820,16 @@
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8117770767613038</v>
+        <v>0.8081023454157783</v>
       </c>
       <c r="J11" t="n">
-        <v>0.772</v>
+        <v>0.7782340862422998</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8558758314855875</v>
+        <v>0.8403547671840355</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7696267696267697</v>
+        <v>0.7683397683397684</v>
       </c>
     </row>
     <row r="12">
@@ -2714,17 +2840,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2737,18 +2863,64 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8117770767613038</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8558758314855875</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7696267696267697</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>binary_classification_ConVote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
         <v>8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.7824267782426778</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.7405940594059406</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.8292682926829268</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.7323037323037324</v>
       </c>
     </row>
@@ -2763,66 +2935,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -3066,21 +3238,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>5e-05</v>
@@ -3092,16 +3264,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4148526227392123</v>
+        <v>0.4303984304794021</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4386753849095047</v>
+        <v>0.4649776149776149</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4770467836257309</v>
+        <v>0.4483719983719984</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5773809523809523</v>
       </c>
     </row>
     <row r="8">
@@ -3112,17 +3284,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3135,19 +3307,19 @@
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3487307953484424</v>
+        <v>0.4148526227392123</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3848011710511711</v>
+        <v>0.4386753849095047</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4268750000000001</v>
+        <v>0.4770467836257309</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -3158,7 +3330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3168,7 +3340,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -3181,19 +3353,19 @@
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3315144070390883</v>
+        <v>0.3487307953484424</v>
       </c>
       <c r="J9" t="n">
-        <v>0.339909876448338</v>
+        <v>0.3848011710511711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3829670329670329</v>
+        <v>0.4268750000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.4642857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -3204,21 +3376,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>5e-05</v>
@@ -3230,16 +3402,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3112039516273786</v>
+        <v>0.3315144070390883</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3381018834966203</v>
+        <v>0.339909876448338</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3898809523809524</v>
+        <v>0.3829670329670329</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5059523809523809</v>
+        <v>0.4940476190476191</v>
       </c>
     </row>
     <row r="11">
@@ -3250,21 +3422,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>5e-05</v>
@@ -3273,19 +3445,19 @@
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4121982775852745</v>
+        <v>0.3112039516273786</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4390222350748667</v>
+        <v>0.3381018834966203</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4961361737677527</v>
+        <v>0.3898809523809524</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5476190476190477</v>
+        <v>0.5059523809523809</v>
       </c>
     </row>
     <row r="12">
@@ -3296,17 +3468,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3322,15 +3494,61 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
+        <v>0.4121982775852745</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4390222350748667</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4961361737677527</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5476190476190477</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>multi_class_classification_MotionPolicy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.3693028949607897</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.3828537690379796</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.435077276524645</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.4761904761904762</v>
       </c>
     </row>
@@ -3345,66 +3563,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -3648,21 +3866,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>5e-05</v>
@@ -3674,16 +3892,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8825613605824806</v>
+        <v>0.9240128818284253</v>
       </c>
       <c r="J7" t="n">
-        <v>0.894946804954952</v>
+        <v>0.9353587273858063</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8839874169852274</v>
+        <v>0.9227480577439859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9711215700204244</v>
+        <v>0.9711558547990551</v>
       </c>
     </row>
     <row r="8">
@@ -3694,17 +3912,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3720,16 +3938,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8827257820134612</v>
+        <v>0.8825613605824806</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8948219888515823</v>
+        <v>0.894946804954952</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8846632183497631</v>
+        <v>0.8839874169852274</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9745698268696836</v>
+        <v>0.9711215700204244</v>
       </c>
     </row>
     <row r="9">
@@ -3740,7 +3958,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3750,14 +3968,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
@@ -3766,16 +3984,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9217134408327748</v>
+        <v>0.8827257820134612</v>
       </c>
       <c r="J9" t="n">
-        <v>0.938049277833066</v>
+        <v>0.8948219888515823</v>
       </c>
       <c r="K9" t="n">
-        <v>0.920194778082474</v>
+        <v>0.8846632183497631</v>
       </c>
       <c r="L9" t="n">
-        <v>0.975840667625092</v>
+        <v>0.9745698268696836</v>
       </c>
     </row>
     <row r="10">
@@ -3786,21 +4004,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>3e-05</v>
@@ -3812,16 +4030,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9210096613623362</v>
+        <v>0.9217134408327748</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9346487307972519</v>
+        <v>0.938049277833066</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9213490501594489</v>
+        <v>0.920194778082474</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9715766925278563</v>
+        <v>0.975840667625092</v>
       </c>
     </row>
     <row r="11">
@@ -3832,24 +4050,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -3858,16 +4076,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8831388632954821</v>
+        <v>0.9210096613623362</v>
       </c>
       <c r="J11" t="n">
-        <v>0.883796132913359</v>
+        <v>0.9346487307972519</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8858574006542305</v>
+        <v>0.9213490501594489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9758056032820225</v>
+        <v>0.9715766925278563</v>
       </c>
     </row>
     <row r="12">
@@ -3878,41 +4096,87 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>4</v>
       </c>
       <c r="F12" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8831388632954821</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.883796132913359</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8858574006542305</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9758056032820225</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ner_nerex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
         <v>3e-05</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
         <v>16</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.9167561280495693</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.9267026118685364</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.9220669527378278</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.9706597993073439</v>
       </c>
     </row>
@@ -3927,66 +4191,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -4230,42 +4494,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B32</t>
+          <t>ModernBERT-base-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8159956768440962</v>
+        <v>0.8125525357242925</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7868681605002605</v>
+        <v>0.8114157806379407</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8473625140291807</v>
+        <v>0.813692480359147</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7964125560538117</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -4276,24 +4540,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
@@ -4302,16 +4566,16 @@
         <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8148959474260679</v>
+        <v>0.8159956768440962</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7957219251336899</v>
+        <v>0.7868681605002605</v>
       </c>
       <c r="K8" t="n">
-        <v>0.835016835016835</v>
+        <v>0.8473625140291807</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7979073243647234</v>
+        <v>0.7964125560538117</v>
       </c>
     </row>
     <row r="9">
@@ -4322,7 +4586,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4332,32 +4596,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7244444444444444</v>
+        <v>0.8148959474260679</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7172717271727173</v>
+        <v>0.7957219251336899</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7317620650953984</v>
+        <v>0.835016835016835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7034379671150972</v>
+        <v>0.7979073243647234</v>
       </c>
     </row>
     <row r="10">
@@ -4368,21 +4632,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>2e-05</v>
@@ -4391,19 +4655,19 @@
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7741398446170921</v>
+        <v>0.7244444444444444</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7656421514818881</v>
+        <v>0.7172717271727173</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7828282828282829</v>
+        <v>0.7317620650953984</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7566517189835575</v>
+        <v>0.7034379671150972</v>
       </c>
     </row>
     <row r="11">
@@ -4414,21 +4678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>2e-05</v>
@@ -4440,16 +4704,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8141496598639456</v>
+        <v>0.7741398446170921</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7902799788695193</v>
+        <v>0.7656421514818881</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8395061728395061</v>
+        <v>0.7828282828282829</v>
       </c>
       <c r="L11" t="n">
-        <v>0.795814648729447</v>
+        <v>0.7566517189835575</v>
       </c>
     </row>
     <row r="12">
@@ -4460,17 +4724,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4486,15 +4750,61 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
+        <v>0.8141496598639456</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7902799788695193</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8395061728395061</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.795814648729447</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>binary_classification_ParlVote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.7453450164293538</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.727807486631016</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.7637485970819304</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.7219730941704036</v>
       </c>
     </row>
@@ -4509,66 +4819,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -4812,17 +5122,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4838,16 +5148,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221156836134196</v>
+        <v>0.6225391269065159</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6081505841196378</v>
+        <v>0.6265570432205897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6522854629717133</v>
+        <v>0.6293126587218392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6714159821867033</v>
+        <v>0.6768704630938406</v>
       </c>
     </row>
     <row r="8">
@@ -4858,17 +5168,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4884,16 +5194,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6272710719880208</v>
+        <v>0.6221156836134196</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6145569353889517</v>
+        <v>0.6081505841196378</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6566326550508595</v>
+        <v>0.6522854629717133</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6771857804759007</v>
+        <v>0.6714159821867033</v>
       </c>
     </row>
     <row r="9">
@@ -4904,7 +5214,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4914,7 +5224,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4930,16 +5240,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6133000895001974</v>
+        <v>0.6272710719880208</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6102824539795031</v>
+        <v>0.6145569353889517</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6299802229719957</v>
+        <v>0.6566326550508595</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6654877943586647</v>
+        <v>0.6771857804759007</v>
       </c>
     </row>
     <row r="10">
@@ -4950,17 +5260,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH2-LR5e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4973,19 +5283,19 @@
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.634153819234582</v>
+        <v>0.6133000895001974</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6236959639469122</v>
+        <v>0.6102824539795031</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6518806555843227</v>
+        <v>0.6299802229719957</v>
       </c>
       <c r="L10" t="n">
-        <v>0.696672137064099</v>
+        <v>0.6654877943586647</v>
       </c>
     </row>
     <row r="11">
@@ -4996,21 +5306,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B32</t>
+          <t>ConfliBERT-scr-uncased-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>5e-05</v>
@@ -5019,19 +5329,19 @@
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6319123355121764</v>
+        <v>0.634153819234582</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6218778982190629</v>
+        <v>0.6236959639469122</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6489354475656615</v>
+        <v>0.6518806555843227</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6927058105355354</v>
+        <v>0.696672137064099</v>
       </c>
     </row>
     <row r="12">
@@ -5042,17 +5352,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -5065,18 +5375,64 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
+        <v>32</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6319123355121764</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6218778982190629</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6489354475656615</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6927058105355354</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sequence_labelling_ElecDeb60to20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
         <v>8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.6139953920395655</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.6021395014625408</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.6360621813084459</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.6684964312862842</v>
       </c>
     </row>
@@ -5091,66 +5447,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -5394,17 +5750,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -5420,16 +5776,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6235190327793332</v>
+        <v>0.6118017621497291</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6303333480007958</v>
+        <v>0.6303945339219652</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6213583693316345</v>
+        <v>0.5959831965159648</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6618150061858671</v>
+        <v>0.6676580810183809</v>
       </c>
     </row>
     <row r="8">
@@ -5440,24 +5796,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
@@ -5466,16 +5822,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6202426129404419</v>
+        <v>0.6235190327793332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6331356704592661</v>
+        <v>0.6303333480007958</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6226674317494432</v>
+        <v>0.6213583693316345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6695406570536644</v>
+        <v>0.6618150061858671</v>
       </c>
     </row>
     <row r="9">
@@ -5486,7 +5842,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5496,14 +5852,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
@@ -5512,16 +5868,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6234966293348686</v>
+        <v>0.6202426129404419</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6345216359930843</v>
+        <v>0.6331356704592661</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6141281667772459</v>
+        <v>0.6226674317494432</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6588151826888967</v>
+        <v>0.6695406570536644</v>
       </c>
     </row>
     <row r="10">
@@ -5532,24 +5888,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
@@ -5558,16 +5914,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6255443714448506</v>
+        <v>0.6234966293348686</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6406401224611039</v>
+        <v>0.6345216359930843</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6198594481013893</v>
+        <v>0.6141281667772459</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6641498036846875</v>
+        <v>0.6588151826888967</v>
       </c>
     </row>
     <row r="11">
@@ -5578,24 +5934,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -5604,16 +5960,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6199564388184508</v>
+        <v>0.6255443714448506</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6254657529405155</v>
+        <v>0.6406401224611039</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6167435054074607</v>
+        <v>0.6198594481013893</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6669031571479248</v>
+        <v>0.6641498036846875</v>
       </c>
     </row>
     <row r="12">
@@ -5624,41 +5980,87 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6199564388184508</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6254657529405155</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6167435054074607</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6669031571479248</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sequence_labelling_ArgUNSC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>bert-base-uncased</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>uncased</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>3e-05</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
         <v>16</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.620254463306098</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.6256634236982854</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.6215063210129829</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.6632705043301069</v>
       </c>
     </row>
@@ -5673,66 +6075,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -5976,42 +6378,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR3e-05-WD0.1-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>3e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6161844759507634</v>
+        <v>0.6536875104815234</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6261844733242263</v>
+        <v>0.6539589404360659</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6093547713635835</v>
+        <v>0.6534776115381911</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7071812214044162</v>
+        <v>0.7380147205092501</v>
       </c>
     </row>
     <row r="8">
@@ -6022,24 +6424,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
@@ -6048,16 +6450,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6356679047364483</v>
+        <v>0.6161844759507634</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6422787052556931</v>
+        <v>0.6261844733242263</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6309959829413968</v>
+        <v>0.6093547713635835</v>
       </c>
       <c r="L8" t="n">
-        <v>0.723095285458524</v>
+        <v>0.7071812214044162</v>
       </c>
     </row>
     <row r="9">
@@ -6068,7 +6470,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6078,11 +6480,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>2e-05</v>
@@ -6091,19 +6493,19 @@
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6010133140246318</v>
+        <v>0.6356679047364483</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6022243748225815</v>
+        <v>0.6422787052556931</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6001102242493958</v>
+        <v>0.6309959829413968</v>
       </c>
       <c r="L9" t="n">
-        <v>0.696240302367217</v>
+        <v>0.723095285458524</v>
       </c>
     </row>
     <row r="10">
@@ -6114,42 +6516,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6231946321440852</v>
+        <v>0.6010133140246318</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6287241517446706</v>
+        <v>0.6022243748225815</v>
       </c>
       <c r="K10" t="n">
-        <v>0.619733011029279</v>
+        <v>0.6001102242493958</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7153371792321465</v>
+        <v>0.696240302367217</v>
       </c>
     </row>
     <row r="11">
@@ -6160,42 +6562,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6132418348757264</v>
+        <v>0.6231946321440852</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6259099894322943</v>
+        <v>0.6287241517446706</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6063330820524419</v>
+        <v>0.619733011029279</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7023075392878456</v>
+        <v>0.7153371792321465</v>
       </c>
     </row>
     <row r="12">
@@ -6206,24 +6608,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
@@ -6232,15 +6634,61 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
+        <v>0.6132418348757264</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6259099894322943</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6063330820524419</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7023075392878456</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ElecDeb60to20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR2e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.5973218502362674</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.6009831759396437</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.5941854600135872</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.6973343942709369</v>
       </c>
     </row>
@@ -6255,66 +6703,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weight_decay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>batch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_precision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>test_recall</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
@@ -6558,42 +7006,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR3e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6477541371158393</v>
+        <v>0.6751152073732719</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6431924882629108</v>
+        <v>0.6540178571428571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6523809523809524</v>
+        <v>0.6976190476190476</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6169665809768637</v>
+        <v>0.6375321336760925</v>
       </c>
     </row>
     <row r="8">
@@ -6604,21 +7052,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>3e-05</v>
@@ -6630,16 +7078,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6460396039603961</v>
+        <v>0.6477541371158393</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6726804123711341</v>
+        <v>0.6431924882629108</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6214285714285714</v>
+        <v>0.6523809523809524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6323907455012854</v>
+        <v>0.6169665809768637</v>
       </c>
     </row>
     <row r="9">
@@ -6650,7 +7098,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6660,32 +7108,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH3-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6090047393364929</v>
+        <v>0.6460396039603961</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6061320754716981</v>
+        <v>0.6726804123711341</v>
       </c>
       <c r="K9" t="n">
-        <v>0.611904761904762</v>
+        <v>0.6214285714285714</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5758354755784062</v>
+        <v>0.6323907455012854</v>
       </c>
     </row>
     <row r="10">
@@ -6696,42 +7144,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
+          <t>bert-base-cased-EPOCH3-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6370370370370371</v>
+        <v>0.6090047393364929</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.6061320754716981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.611904761904762</v>
       </c>
       <c r="L10" t="n">
-        <v>0.622107969151671</v>
+        <v>0.5758354755784062</v>
       </c>
     </row>
     <row r="11">
@@ -6742,42 +7190,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6706021251475797</v>
+        <v>0.6370370370370371</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6651053864168618</v>
+        <v>0.6615384615384615</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6761904761904762</v>
+        <v>0.6142857142857143</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6413881748071979</v>
+        <v>0.622107969151671</v>
       </c>
     </row>
     <row r="12">
@@ -6788,17 +7236,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>NEWRooseBERT-cont-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -6814,15 +7262,61 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
+        <v>0.6706021251475797</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6651053864168618</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6761904761904762</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6413881748071979</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>binary_classification_AusHansard</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.6463547334058759</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0.5951903807615231</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0.7071428571428572</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>0.5822622107969152</v>
       </c>
     </row>

--- a/logs/encoders/best_results.xlsx
+++ b/logs/encoders/best_results.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,24 +588,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>deberta-base-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.01</v>
@@ -614,16 +614,16 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5836349787290027</v>
+        <v>0.5555068972553053</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5781539679196633</v>
+        <v>0.5325843661626448</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6046143259433039</v>
+        <v>0.5970771752125014</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5881845623113411</v>
+        <v>0.5502371711944803</v>
       </c>
     </row>
     <row r="5">
@@ -634,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>ConfliBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -657,19 +657,19 @@
         <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5687566614664791</v>
+        <v>0.5836349787290027</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5486424732623996</v>
+        <v>0.5781539679196633</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6062592535454433</v>
+        <v>0.6046143259433039</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5739542906425183</v>
+        <v>0.5881845623113411</v>
       </c>
     </row>
     <row r="6">
@@ -680,7 +680,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -703,19 +703,19 @@
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5710856732204026</v>
+        <v>0.5687566614664791</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5615697761201441</v>
+        <v>0.5486424732623996</v>
       </c>
       <c r="K6" t="n">
-        <v>0.597333758257375</v>
+        <v>0.6062592535454433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5817162570073308</v>
+        <v>0.5739542906425183</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -736,14 +736,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
@@ -752,16 +752,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6551323184095549</v>
+        <v>0.5594042383359413</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6740048850414965</v>
+        <v>0.5442280005461474</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6435763768444689</v>
+        <v>0.5884322356177354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6774471755066839</v>
+        <v>0.5657611039241052</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -798,16 +798,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6366429649879222</v>
+        <v>0.5710856732204026</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6289021744157345</v>
+        <v>0.5615697761201441</v>
       </c>
       <c r="K8" t="n">
-        <v>0.655468180582409</v>
+        <v>0.597333758257375</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6511427339370418</v>
+        <v>0.5817162570073308</v>
       </c>
     </row>
     <row r="9">
@@ -818,21 +818,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>5e-05</v>
@@ -844,16 +844,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.605729002653374</v>
+        <v>0.6551323184095549</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6020543615306304</v>
+        <v>0.6740048850414965</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6254756396315163</v>
+        <v>0.6435763768444689</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6269943941354031</v>
+        <v>0.6774471755066839</v>
       </c>
     </row>
     <row r="10">
@@ -864,17 +864,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -890,16 +890,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5622471320695576</v>
+        <v>0.6366429649879222</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5524602146219695</v>
+        <v>0.6289021744157345</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5872398116363503</v>
+        <v>0.655468180582409</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5610176800344976</v>
+        <v>0.6511427339370418</v>
       </c>
     </row>
     <row r="11">
@@ -910,24 +910,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -936,16 +936,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6019257476788826</v>
+        <v>0.605729002653374</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5845956835229789</v>
+        <v>0.6020543615306304</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6314118142374329</v>
+        <v>0.6254756396315163</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6093143596377749</v>
+        <v>0.6269943941354031</v>
       </c>
     </row>
     <row r="12">
@@ -956,7 +956,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -982,16 +982,16 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.615202141029628</v>
+        <v>0.5622471320695576</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6065731961977764</v>
+        <v>0.5524602146219695</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6385201364274612</v>
+        <v>0.5872398116363503</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6269943941354031</v>
+        <v>0.5610176800344976</v>
       </c>
     </row>
     <row r="13">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1012,31 +1012,123 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6019257476788826</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5845956835229789</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6314118142374329</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6093143596377749</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ParlVotePlus</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.615202141029628</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6065731961977764</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6385201364274612</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6269943941354031</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ParlVotePlus</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.5605635830057274</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.5409538629798983</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.5991212059138304</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.5623113410952997</v>
       </c>
     </row>
@@ -1051,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,42 +1308,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>deberta-base-EPOCH4-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6652331795188938</v>
+        <v>0.7353186478928518</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6858877044056197</v>
+        <v>0.7214598483071389</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6497951527216027</v>
+        <v>0.7514397819655297</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7853231106243155</v>
+        <v>0.8170865279299014</v>
       </c>
     </row>
     <row r="5">
@@ -1262,17 +1354,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>ConfliBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1285,19 +1377,19 @@
         <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6500041688123789</v>
+        <v>0.6652331795188938</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6328386640857837</v>
+        <v>0.6858877044056197</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6726204171391802</v>
+        <v>0.6497951527216027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7491785323110625</v>
+        <v>0.7853231106243155</v>
       </c>
     </row>
     <row r="6">
@@ -1308,7 +1400,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1318,32 +1410,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6050465886014341</v>
+        <v>0.6500041688123789</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5851555092856622</v>
+        <v>0.6328386640857837</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6636842066641457</v>
+        <v>0.6726204171391802</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6955093099671413</v>
+        <v>0.7491785323110625</v>
       </c>
     </row>
     <row r="7">
@@ -1354,7 +1446,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1364,32 +1456,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>roberta-base-EPOCH3-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7248866732992733</v>
+        <v>0.7286873024640853</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7548958433023895</v>
+        <v>0.7035660208074002</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7013857948093234</v>
+        <v>0.7638197151730242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8138006571741512</v>
+        <v>0.7940854326396495</v>
       </c>
     </row>
     <row r="8">
@@ -1400,7 +1492,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1410,32 +1502,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6992540673408048</v>
+        <v>0.6050465886014341</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7000680580762251</v>
+        <v>0.5851555092856622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7007912769587544</v>
+        <v>0.6636842066641457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7973713033953997</v>
+        <v>0.6955093099671413</v>
       </c>
     </row>
     <row r="9">
@@ -1446,42 +1538,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7377515144696555</v>
+        <v>0.7248866732992733</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7279519463985483</v>
+        <v>0.7548958433023895</v>
       </c>
       <c r="K9" t="n">
-        <v>0.750050733705162</v>
+        <v>0.7013857948093234</v>
       </c>
       <c r="L9" t="n">
-        <v>0.828039430449069</v>
+        <v>0.8138006571741512</v>
       </c>
     </row>
     <row r="10">
@@ -1492,42 +1584,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6096839627754294</v>
+        <v>0.6992540673408048</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5986119567289657</v>
+        <v>0.7000680580762251</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6324078271668098</v>
+        <v>0.7007912769587544</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6889375684556407</v>
+        <v>0.7973713033953997</v>
       </c>
     </row>
     <row r="11">
@@ -1538,42 +1630,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7280923536795578</v>
+        <v>0.7377515144696555</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7109206191774998</v>
+        <v>0.7279519463985483</v>
       </c>
       <c r="K11" t="n">
-        <v>0.753583033428138</v>
+        <v>0.750050733705162</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7776560788608982</v>
+        <v>0.828039430449069</v>
       </c>
     </row>
     <row r="12">
@@ -1584,7 +1676,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1594,32 +1686,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7126718452497252</v>
+        <v>0.6096839627754294</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7013451199956832</v>
+        <v>0.5986119567289657</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7299249894457659</v>
+        <v>0.6324078271668098</v>
       </c>
       <c r="L12" t="n">
-        <v>0.787513691128149</v>
+        <v>0.6889375684556407</v>
       </c>
     </row>
     <row r="13">
@@ -1630,41 +1722,133 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>ConfliBERT-scr-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7280923536795578</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7109206191774998</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.753583033428138</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7776560788608982</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ArgUNSC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7126718452497252</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7013451199956832</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7299249894457659</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.787513691128149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ArgUNSC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>bert-base-uncased</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>uncased</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>3e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.6377004432695424</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.6296793169103069</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.648109462457805</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.7437020810514786</v>
       </c>
     </row>
@@ -1679,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1844,42 +2028,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B32</t>
+          <t>deberta-base-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7852760736196319</v>
+        <v>0.7516778523489933</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9552238805970149</v>
+        <v>0.835820895522388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.717741935483871</v>
+        <v>0.7016129032258065</v>
       </c>
     </row>
     <row r="5">
@@ -1890,21 +2074,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>ConfliBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>5e-05</v>
@@ -1916,16 +2100,16 @@
         <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.7852760736196319</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.9552238805970149</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.717741935483871</v>
       </c>
     </row>
     <row r="6">
@@ -1936,7 +2120,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1946,11 +2130,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>5e-05</v>
@@ -1959,19 +2143,19 @@
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8059701492537313</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6935483870967742</v>
       </c>
     </row>
     <row r="7">
@@ -1982,7 +2166,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1992,14 +2176,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
@@ -2008,16 +2192,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.75177304964539</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7162162162162162</v>
+        <v>0.6588235294117647</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7910447761194029</v>
+        <v>0.835820895522388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.717741935483871</v>
+        <v>0.6774193548387096</v>
       </c>
     </row>
     <row r="8">
@@ -2028,7 +2212,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2038,11 +2222,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>5e-05</v>
@@ -2054,16 +2238,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7669172932330827</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7611940298507462</v>
+        <v>0.8059701492537313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.75</v>
+        <v>0.6774193548387096</v>
       </c>
     </row>
     <row r="9">
@@ -2074,24 +2258,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
@@ -2100,16 +2284,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7518796992481203</v>
+        <v>0.75177304964539</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7162162162162162</v>
       </c>
       <c r="K9" t="n">
-        <v>0.746268656716418</v>
+        <v>0.7910447761194029</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7338709677419355</v>
+        <v>0.717741935483871</v>
       </c>
     </row>
     <row r="10">
@@ -2120,42 +2304,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.765625</v>
+        <v>0.7669172932330827</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7313432835820896</v>
+        <v>0.7611940298507462</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -2166,24 +2350,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -2192,16 +2376,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.7518796992481203</v>
       </c>
       <c r="J11" t="n">
-        <v>0.675</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8059701492537313</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6854838709677419</v>
+        <v>0.7338709677419355</v>
       </c>
     </row>
     <row r="12">
@@ -2212,7 +2396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2222,14 +2406,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
@@ -2238,16 +2422,16 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.765625</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7397260273972602</v>
+        <v>0.8032786885245902</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8059701492537313</v>
+        <v>0.7313432835820896</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7580645161290323</v>
       </c>
     </row>
     <row r="13">
@@ -2258,7 +2442,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2268,31 +2452,123 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7346938775510204</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8059701492537313</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6854838709677419</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>binary_classification_HanDeSet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
         <v>3e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7397260273972602</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8059701492537313</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>binary_classification_HanDeSet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>32</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.7549668874172185</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.6785714285714286</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.8507462686567164</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.7016129032258065</v>
       </c>
     </row>
@@ -2307,7 +2583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2472,42 +2748,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>deberta-base-EPOCH4-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8146596858638744</v>
+        <v>0.818848167539267</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7718253968253969</v>
+        <v>0.7757936507936508</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8625277161862528</v>
+        <v>0.8669623059866962</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7722007722007722</v>
+        <v>0.7773487773487774</v>
       </c>
     </row>
     <row r="5">
@@ -2518,17 +2794,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>ConfliBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2541,19 +2817,19 @@
         <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8008611410118407</v>
+        <v>0.8146596858638744</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7782426778242678</v>
+        <v>0.7718253968253969</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8248337028824834</v>
+        <v>0.8625277161862528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7722007722007722</v>
       </c>
     </row>
     <row r="6">
@@ -2564,7 +2840,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2574,32 +2850,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>ConfliBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8081023454157783</v>
+        <v>0.8008611410118407</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7782340862422998</v>
+        <v>0.7782426778242678</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8403547671840355</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7683397683397684</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="7">
@@ -2610,7 +2886,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2620,32 +2896,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH2-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8268041237113402</v>
+        <v>0.8154327424400417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7726396917148363</v>
+        <v>0.7696850393700787</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8891352549889135</v>
+        <v>0.8669623059866962</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.7722007722007722</v>
       </c>
     </row>
     <row r="8">
@@ -2656,7 +2932,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2666,32 +2942,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8162393162393162</v>
+        <v>0.8081023454157783</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7876288659793814</v>
+        <v>0.7782340862422998</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8470066518847007</v>
+        <v>0.8403547671840355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7786357786357786</v>
+        <v>0.7683397683397684</v>
       </c>
     </row>
     <row r="9">
@@ -2702,42 +2978,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B16</t>
+          <t>ModernBERT-base-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7986870897155361</v>
+        <v>0.8268041237113402</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7883369330453563</v>
+        <v>0.7726396917148363</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8093126385809313</v>
+        <v>0.8891352549889135</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7631917631917632</v>
+        <v>0.7837837837837838</v>
       </c>
     </row>
     <row r="10">
@@ -2748,42 +3024,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7694038245219348</v>
+        <v>0.8162393162393162</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7808219178082192</v>
+        <v>0.7876288659793814</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7583148558758315</v>
+        <v>0.8470066518847007</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7361647361647362</v>
+        <v>0.7786357786357786</v>
       </c>
     </row>
     <row r="11">
@@ -2794,24 +3070,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -2820,16 +3096,16 @@
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8081023454157783</v>
+        <v>0.7986870897155361</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7782340862422998</v>
+        <v>0.7883369330453563</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8403547671840355</v>
+        <v>0.8093126385809313</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7683397683397684</v>
+        <v>0.7631917631917632</v>
       </c>
     </row>
     <row r="12">
@@ -2840,7 +3116,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2850,7 +3126,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2866,16 +3142,16 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8117770767613038</v>
+        <v>0.7694038245219348</v>
       </c>
       <c r="J12" t="n">
-        <v>0.772</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8558758314855875</v>
+        <v>0.7583148558758315</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7696267696267697</v>
+        <v>0.7361647361647362</v>
       </c>
     </row>
     <row r="13">
@@ -2886,41 +3162,133 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>ConfliBERT-scr-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8081023454157783</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7782340862422998</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8403547671840355</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7683397683397684</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>binary_classification_ConVote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8117770767613038</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8558758314855875</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7696267696267697</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>binary_classification_ConVote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>bert-base-uncased</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>uncased</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>3e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.7824267782426778</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.7405940594059406</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.8292682926829268</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.7323037323037324</v>
       </c>
     </row>
@@ -2935,7 +3303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3100,17 +3468,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>deberta-base-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -3126,16 +3494,16 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3896149363302802</v>
+        <v>0.3316815049951571</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3769073032230927</v>
+        <v>0.3294945794945796</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4592314118629909</v>
+        <v>0.413044363044363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5773809523809523</v>
+        <v>0.5178571428571429</v>
       </c>
     </row>
     <row r="5">
@@ -3146,17 +3514,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>ConfliBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -3169,19 +3537,19 @@
         <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3872642949100076</v>
+        <v>0.3896149363302802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4051982374350795</v>
+        <v>0.3769073032230927</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4587719298245614</v>
+        <v>0.4592314118629909</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.5773809523809523</v>
       </c>
     </row>
     <row r="6">
@@ -3192,7 +3560,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3202,7 +3570,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -3215,19 +3583,19 @@
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3058847798723217</v>
+        <v>0.3872642949100076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2878138328276832</v>
+        <v>0.4051982374350795</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4007727652464494</v>
+        <v>0.4587719298245614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5654761904761905</v>
+        <v>0.4821428571428572</v>
       </c>
     </row>
     <row r="7">
@@ -3238,7 +3606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3248,14 +3616,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
@@ -3264,16 +3632,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4303984304794021</v>
+        <v>0.3335314300833869</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4649776149776149</v>
+        <v>0.3556377383300461</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4483719983719984</v>
+        <v>0.4042836792836793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5773809523809523</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -3284,7 +3652,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3294,7 +3662,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3310,16 +3678,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4148526227392123</v>
+        <v>0.3058847798723217</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4386753849095047</v>
+        <v>0.2878138328276832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4770467836257309</v>
+        <v>0.4007727652464494</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5654761904761905</v>
       </c>
     </row>
     <row r="9">
@@ -3330,21 +3698,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B32</t>
+          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>5e-05</v>
@@ -3353,19 +3721,19 @@
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3487307953484424</v>
+        <v>0.4303984304794021</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3848011710511711</v>
+        <v>0.4649776149776149</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4268750000000001</v>
+        <v>0.4483719983719984</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.5773809523809523</v>
       </c>
     </row>
     <row r="10">
@@ -3376,17 +3744,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -3402,16 +3770,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3315144070390883</v>
+        <v>0.4148526227392123</v>
       </c>
       <c r="J10" t="n">
-        <v>0.339909876448338</v>
+        <v>0.4386753849095047</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3829670329670329</v>
+        <v>0.4770467836257309</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -3422,21 +3790,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>5e-05</v>
@@ -3445,19 +3813,19 @@
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3112039516273786</v>
+        <v>0.3487307953484424</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3381018834966203</v>
+        <v>0.3848011710511711</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3898809523809524</v>
+        <v>0.4268750000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5059523809523809</v>
+        <v>0.4642857142857143</v>
       </c>
     </row>
     <row r="12">
@@ -3468,7 +3836,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3478,7 +3846,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3491,19 +3859,19 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4121982775852745</v>
+        <v>0.3315144070390883</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4390222350748667</v>
+        <v>0.339909876448338</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4961361737677527</v>
+        <v>0.3829670329670329</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5476190476190477</v>
+        <v>0.4940476190476191</v>
       </c>
     </row>
     <row r="13">
@@ -3514,7 +3882,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3524,11 +3892,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>5e-05</v>
@@ -3537,18 +3905,110 @@
         <v>0.01</v>
       </c>
       <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3112039516273786</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3381018834966203</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3898809523809524</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5059523809523809</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>multi_class_classification_MotionPolicy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
+        <v>0.4121982775852745</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4390222350748667</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4961361737677527</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5476190476190477</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>multi_class_classification_MotionPolicy</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR5e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.3693028949607897</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.3828537690379796</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.435077276524645</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.4761904761904762</v>
       </c>
     </row>
@@ -3563,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3728,17 +4188,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>deberta-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -3754,16 +4214,16 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9184800023252506</v>
+        <v>0.9267506049363716</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9307219659116078</v>
+        <v>0.9426072990760557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9201244737960881</v>
+        <v>0.9251999338416291</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9753672989936534</v>
+        <v>0.9768535132419436</v>
       </c>
     </row>
     <row r="5">
@@ -3774,17 +4234,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -3800,16 +4260,16 @@
         <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9180865837965417</v>
+        <v>0.9184800023252506</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9243789196411601</v>
+        <v>0.9307219659116078</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9202491209955241</v>
+        <v>0.9201244737960881</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9713346949649232</v>
+        <v>0.9753672989936534</v>
       </c>
     </row>
     <row r="6">
@@ -3820,7 +4280,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3830,11 +4290,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>5e-05</v>
@@ -3846,16 +4306,16 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8779157784486221</v>
+        <v>0.9180865837965417</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8920144475326731</v>
+        <v>0.9243789196411601</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8811207533168123</v>
+        <v>0.9202491209955241</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9703166226912929</v>
+        <v>0.9713346949649232</v>
       </c>
     </row>
     <row r="7">
@@ -3866,7 +4326,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3876,11 +4336,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>5e-05</v>
@@ -3892,16 +4352,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9240128818284253</v>
+        <v>0.9255779290886258</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9353587273858063</v>
+        <v>0.9415172303686516</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9227480577439859</v>
+        <v>0.9239181008734123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9711558547990551</v>
+        <v>0.976548482021101</v>
       </c>
     </row>
     <row r="8">
@@ -3912,7 +4372,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3922,7 +4382,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3938,16 +4398,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8825613605824806</v>
+        <v>0.8779157784486221</v>
       </c>
       <c r="J8" t="n">
-        <v>0.894946804954952</v>
+        <v>0.8920144475326731</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8839874169852274</v>
+        <v>0.8811207533168123</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9711215700204244</v>
+        <v>0.9703166226912929</v>
       </c>
     </row>
     <row r="9">
@@ -3958,21 +4418,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH3-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>5e-05</v>
@@ -3984,16 +4444,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8827257820134612</v>
+        <v>0.9240128818284253</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8948219888515823</v>
+        <v>0.9353587273858063</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8846632183497631</v>
+        <v>0.9227480577439859</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9745698268696836</v>
+        <v>0.9711558547990551</v>
       </c>
     </row>
     <row r="10">
@@ -4004,24 +4464,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
@@ -4030,16 +4490,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9217134408327748</v>
+        <v>0.8825613605824806</v>
       </c>
       <c r="J10" t="n">
-        <v>0.938049277833066</v>
+        <v>0.894946804954952</v>
       </c>
       <c r="K10" t="n">
-        <v>0.920194778082474</v>
+        <v>0.8839874169852274</v>
       </c>
       <c r="L10" t="n">
-        <v>0.975840667625092</v>
+        <v>0.9711215700204244</v>
       </c>
     </row>
     <row r="11">
@@ -4050,24 +4510,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -4076,16 +4536,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9210096613623362</v>
+        <v>0.8827257820134612</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9346487307972519</v>
+        <v>0.8948219888515823</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9213490501594489</v>
+        <v>0.8846632183497631</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9715766925278563</v>
+        <v>0.9745698268696836</v>
       </c>
     </row>
     <row r="12">
@@ -4096,7 +4556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4106,14 +4566,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>5e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
@@ -4122,16 +4582,16 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8831388632954821</v>
+        <v>0.9217134408327748</v>
       </c>
       <c r="J12" t="n">
-        <v>0.883796132913359</v>
+        <v>0.938049277833066</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8858574006542305</v>
+        <v>0.920194778082474</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9758056032820225</v>
+        <v>0.975840667625092</v>
       </c>
     </row>
     <row r="13">
@@ -4142,7 +4602,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4152,7 +4612,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4165,18 +4625,110 @@
         <v>0.01</v>
       </c>
       <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9210096613623362</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9346487307972519</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9213490501594489</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9715766925278563</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ner_nerex</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR5e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8831388632954821</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.883796132913359</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8858574006542305</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9758056032820225</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ner_nerex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.9167561280495693</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.9267026118685364</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.9220669527378278</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.9706597993073439</v>
       </c>
     </row>
@@ -4191,7 +4743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4356,21 +4908,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>deberta-base-EPOCH2-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2e-05</v>
@@ -4379,19 +4931,19 @@
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.783109404990403</v>
+        <v>0.6634858265506596</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7656836461126005</v>
+        <v>0.6636720943290286</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8013468013468014</v>
+        <v>0.6632996632996633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7635276532137518</v>
+        <v>0.6415545590433482</v>
       </c>
     </row>
     <row r="5">
@@ -4402,17 +4954,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>ConfliBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4428,16 +4980,16 @@
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7674678591391839</v>
+        <v>0.783109404990403</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7644766146993318</v>
+        <v>0.7656836461126005</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7704826038159371</v>
+        <v>0.8013468013468014</v>
       </c>
       <c r="L5" t="n">
-        <v>0.751270553064275</v>
+        <v>0.7635276532137518</v>
       </c>
     </row>
     <row r="6">
@@ -4448,7 +5000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4458,7 +5010,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4471,19 +5023,19 @@
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8069226608977826</v>
+        <v>0.7674678591391839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.778705636743215</v>
+        <v>0.7644766146993318</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8372615039281706</v>
+        <v>0.7704826038159371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7865470852017937</v>
+        <v>0.751270553064275</v>
       </c>
     </row>
     <row r="7">
@@ -4494,7 +5046,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4504,14 +5056,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>roberta-base-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
@@ -4520,16 +5072,16 @@
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8125525357242925</v>
+        <v>0.8011950027159153</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8114157806379407</v>
+        <v>0.7763157894736842</v>
       </c>
       <c r="K7" t="n">
-        <v>0.813692480359147</v>
+        <v>0.8277216610549943</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>0.7811659192825112</v>
       </c>
     </row>
     <row r="8">
@@ -4540,7 +5092,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4550,7 +5102,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4563,19 +5115,19 @@
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8159956768440962</v>
+        <v>0.8069226608977826</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7868681605002605</v>
+        <v>0.778705636743215</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8473625140291807</v>
+        <v>0.8372615039281706</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7964125560538117</v>
+        <v>0.7865470852017937</v>
       </c>
     </row>
     <row r="9">
@@ -4586,21 +5138,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
+          <t>ModernBERT-base-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>3e-05</v>
@@ -4609,19 +5161,19 @@
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8148959474260679</v>
+        <v>0.8125525357242925</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7957219251336899</v>
+        <v>0.8114157806379407</v>
       </c>
       <c r="K9" t="n">
-        <v>0.835016835016835</v>
+        <v>0.813692480359147</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7979073243647234</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -4632,17 +5184,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4655,19 +5207,19 @@
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7244444444444444</v>
+        <v>0.8159956768440962</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7172717271727173</v>
+        <v>0.7868681605002605</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7317620650953984</v>
+        <v>0.8473625140291807</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7034379671150972</v>
+        <v>0.7964125560538117</v>
       </c>
     </row>
     <row r="11">
@@ -4678,42 +5230,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7741398446170921</v>
+        <v>0.8148959474260679</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7656421514818881</v>
+        <v>0.7957219251336899</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7828282828282829</v>
+        <v>0.835016835016835</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7566517189835575</v>
+        <v>0.7979073243647234</v>
       </c>
     </row>
     <row r="12">
@@ -4724,7 +5276,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4734,7 +5286,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4747,19 +5299,19 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8141496598639456</v>
+        <v>0.7244444444444444</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7902799788695193</v>
+        <v>0.7172717271727173</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8395061728395061</v>
+        <v>0.7317620650953984</v>
       </c>
       <c r="L12" t="n">
-        <v>0.795814648729447</v>
+        <v>0.7034379671150972</v>
       </c>
     </row>
     <row r="13">
@@ -4770,7 +5322,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4780,11 +5332,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>2e-05</v>
@@ -4796,15 +5348,107 @@
         <v>8</v>
       </c>
       <c r="I13" t="n">
+        <v>0.7741398446170921</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7656421514818881</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7828282828282829</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7566517189835575</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>binary_classification_ParlVote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8141496598639456</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7902799788695193</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8395061728395061</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.795814648729447</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>binary_classification_ParlVote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.7453450164293538</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.727807486631016</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.7637485970819304</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.7219730941704036</v>
       </c>
     </row>
@@ -4819,7 +5463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4984,17 +5628,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B16</t>
+          <t>deberta-base-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -5007,19 +5651,19 @@
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.625301056531088</v>
+        <v>0.6312033705824043</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6190459034700014</v>
+        <v>0.621600669047902</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6423828421560153</v>
+        <v>0.6586411762307509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6820229714217465</v>
+        <v>0.6794961797722177</v>
       </c>
     </row>
     <row r="5">
@@ -5030,17 +5674,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -5053,19 +5697,19 @@
         <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6224576400093735</v>
+        <v>0.625301056531088</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6144662394475526</v>
+        <v>0.6190459034700014</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6419739643575468</v>
+        <v>0.6423828421560153</v>
       </c>
       <c r="L5" t="n">
-        <v>0.673635917203151</v>
+        <v>0.6820229714217465</v>
       </c>
     </row>
     <row r="6">
@@ -5076,7 +5720,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5086,7 +5730,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -5102,16 +5746,16 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6233050398672452</v>
+        <v>0.6224576400093735</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6104044235980104</v>
+        <v>0.6144662394475526</v>
       </c>
       <c r="K6" t="n">
-        <v>0.651731442637565</v>
+        <v>0.6419739643575468</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6746265431265026</v>
+        <v>0.673635917203151</v>
       </c>
     </row>
     <row r="7">
@@ -5122,7 +5766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5132,7 +5776,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -5145,19 +5789,19 @@
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6225391269065159</v>
+        <v>0.6230955007085357</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6265570432205897</v>
+        <v>0.6154382100408554</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6293126587218392</v>
+        <v>0.6467037137191572</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6768704630938406</v>
+        <v>0.6725100361916316</v>
       </c>
     </row>
     <row r="8">
@@ -5168,7 +5812,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5178,7 +5822,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -5194,16 +5838,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6221156836134196</v>
+        <v>0.6233050398672452</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6081505841196378</v>
+        <v>0.6104044235980104</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6522854629717133</v>
+        <v>0.651731442637565</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6714159821867033</v>
+        <v>0.6746265431265026</v>
       </c>
     </row>
     <row r="9">
@@ -5214,17 +5858,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -5240,16 +5884,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6272710719880208</v>
+        <v>0.6225391269065159</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6145569353889517</v>
+        <v>0.6265570432205897</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6566326550508595</v>
+        <v>0.6293126587218392</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6771857804759007</v>
+        <v>0.6768704630938406</v>
       </c>
     </row>
     <row r="10">
@@ -5260,17 +5904,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -5286,16 +5930,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6133000895001974</v>
+        <v>0.6221156836134196</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6102824539795031</v>
+        <v>0.6081505841196378</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6299802229719957</v>
+        <v>0.6522854629717133</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6654877943586647</v>
+        <v>0.6714159821867033</v>
       </c>
     </row>
     <row r="11">
@@ -5306,17 +5950,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH2-LR5e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -5329,19 +5973,19 @@
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.634153819234582</v>
+        <v>0.6272710719880208</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6236959639469122</v>
+        <v>0.6145569353889517</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6518806555843227</v>
+        <v>0.6566326550508595</v>
       </c>
       <c r="L11" t="n">
-        <v>0.696672137064099</v>
+        <v>0.6771857804759007</v>
       </c>
     </row>
     <row r="12">
@@ -5352,7 +5996,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5362,11 +6006,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B32</t>
+          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>5e-05</v>
@@ -5375,19 +6019,19 @@
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6319123355121764</v>
+        <v>0.6133000895001974</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6218778982190629</v>
+        <v>0.6102824539795031</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6489354475656615</v>
+        <v>0.6299802229719957</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6927058105355354</v>
+        <v>0.6654877943586647</v>
       </c>
     </row>
     <row r="13">
@@ -5398,7 +6042,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5408,11 +6052,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-scr-uncased-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>5e-05</v>
@@ -5421,18 +6065,110 @@
         <v>0.01</v>
       </c>
       <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.634153819234582</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6236959639469122</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6518806555843227</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.696672137064099</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sequence_labelling_ElecDeb60to20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B32</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>32</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6319123355121764</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6218778982190629</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6489354475656615</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6927058105355354</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sequence_labelling_ElecDeb60to20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR5e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.6139953920395655</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.6021395014625408</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.6360621813084459</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.6684964312862842</v>
       </c>
     </row>
@@ -5447,7 +6183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5612,42 +6348,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B32</t>
+          <t>deberta-base-EPOCH3-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6274948373124069</v>
+        <v>0.6180144927192461</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6437374704304742</v>
+        <v>0.63542154314982</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6157757087846475</v>
+        <v>0.6086552409036133</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6603760198652004</v>
+        <v>0.6656010705523753</v>
       </c>
     </row>
     <row r="5">
@@ -5658,21 +6394,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B32</t>
+          <t>ConfliBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>5e-05</v>
@@ -5684,16 +6420,16 @@
         <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6142706085271419</v>
+        <v>0.6274948373124069</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6309779781491873</v>
+        <v>0.6437374704304742</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6053494907895779</v>
+        <v>0.6157757087846475</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6603595080416272</v>
+        <v>0.6603760198652004</v>
       </c>
     </row>
     <row r="6">
@@ -5704,7 +6440,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5714,11 +6450,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>5e-05</v>
@@ -5727,19 +6463,19 @@
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6194119932075783</v>
+        <v>0.6142706085271419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6231702214773522</v>
+        <v>0.6309779781491873</v>
       </c>
       <c r="K6" t="n">
-        <v>0.621409678393518</v>
+        <v>0.6053494907895779</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6601621134794357</v>
+        <v>0.6603595080416272</v>
       </c>
     </row>
     <row r="7">
@@ -5750,7 +6486,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5760,7 +6496,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>roberta-base-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -5773,19 +6509,19 @@
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6118017621497291</v>
+        <v>0.6216005216779701</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6303945339219652</v>
+        <v>0.6368709903126735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5959831965159648</v>
+        <v>0.6114549723015474</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6676580810183809</v>
+        <v>0.6656010705523753</v>
       </c>
     </row>
     <row r="8">
@@ -5796,7 +6532,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5806,11 +6542,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>5e-05</v>
@@ -5822,16 +6558,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6235190327793332</v>
+        <v>0.6194119932075783</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6303333480007958</v>
+        <v>0.6231702214773522</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6213583693316345</v>
+        <v>0.621409678393518</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6618150061858671</v>
+        <v>0.6601621134794357</v>
       </c>
     </row>
     <row r="9">
@@ -5842,24 +6578,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
@@ -5868,16 +6604,16 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6202426129404419</v>
+        <v>0.6118017621497291</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6331356704592661</v>
+        <v>0.6303945339219652</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6226674317494432</v>
+        <v>0.5959831965159648</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6695406570536644</v>
+        <v>0.6676580810183809</v>
       </c>
     </row>
     <row r="10">
@@ -5888,17 +6624,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -5914,16 +6650,16 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6234966293348686</v>
+        <v>0.6235190327793332</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6345216359930843</v>
+        <v>0.6303333480007958</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6141281667772459</v>
+        <v>0.6213583693316345</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6588151826888967</v>
+        <v>0.6618150061858671</v>
       </c>
     </row>
     <row r="11">
@@ -5934,24 +6670,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -5960,16 +6696,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6255443714448506</v>
+        <v>0.6202426129404419</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6406401224611039</v>
+        <v>0.6331356704592661</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6198594481013893</v>
+        <v>0.6226674317494432</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6641498036846875</v>
+        <v>0.6695406570536644</v>
       </c>
     </row>
     <row r="12">
@@ -5980,7 +6716,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5990,7 +6726,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+          <t>bert-base-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -6006,16 +6742,16 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6199564388184508</v>
+        <v>0.6234966293348686</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6254657529405155</v>
+        <v>0.6345216359930843</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6167435054074607</v>
+        <v>0.6141281667772459</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6669031571479248</v>
+        <v>0.6588151826888967</v>
       </c>
     </row>
     <row r="13">
@@ -6026,7 +6762,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6036,31 +6772,123 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>3</v>
       </c>
       <c r="F13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6255443714448506</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6406401224611039</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6198594481013893</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6641498036846875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sequence_labelling_ArgUNSC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH2-LR5e-5-WD0.01-B8</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6199564388184508</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6254657529405155</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6167435054074607</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6669031571479248</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sequence_labelling_ArgUNSC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR3e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
         <v>3e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.620254463306098</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.6256634236982854</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.6215063210129829</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.6632705043301069</v>
       </c>
     </row>
@@ -6075,7 +6903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6240,17 +7068,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>deberta-base-EPOCH3-LR3e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -6263,19 +7091,19 @@
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6077425873406498</v>
+        <v>0.643809400098868</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6114583038712365</v>
+        <v>0.6428711211934058</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6058978255932105</v>
+        <v>0.6468485027507113</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6981300974736423</v>
+        <v>0.7237915257608912</v>
       </c>
     </row>
     <row r="5">
@@ -6286,24 +7114,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G5" t="n">
         <v>0.01</v>
@@ -6312,16 +7140,16 @@
         <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6122457075664108</v>
+        <v>0.6077425873406498</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6254386369700069</v>
+        <v>0.6114583038712365</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6030357022558486</v>
+        <v>0.6058978255932105</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7108613487169286</v>
+        <v>0.6981300974736423</v>
       </c>
     </row>
     <row r="6">
@@ -6332,7 +7160,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6342,11 +7170,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
+          <t>ConfliBERT-cont-uncased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>2e-05</v>
@@ -6358,16 +7186,16 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6133003023736916</v>
+        <v>0.6122457075664108</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6175504470011256</v>
+        <v>0.6254386369700069</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6121900243379701</v>
+        <v>0.6030357022558486</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7018102247861547</v>
+        <v>0.7108613487169286</v>
       </c>
     </row>
     <row r="7">
@@ -6378,7 +7206,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6388,32 +7216,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH2-LR3e-05-WD0.1-B16</t>
+          <t>roberta-base-EPOCH3-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H7" t="n">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6536875104815234</v>
+        <v>0.6458964254936822</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6539589404360659</v>
+        <v>0.6460858624062388</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6534776115381911</v>
+        <v>0.646277009436301</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7380147205092501</v>
+        <v>0.7298587626815198</v>
       </c>
     </row>
     <row r="8">
@@ -6424,7 +7252,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6434,14 +7262,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
@@ -6450,16 +7278,16 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6161844759507634</v>
+        <v>0.6133003023736916</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6261844733242263</v>
+        <v>0.6175504470011256</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6093547713635835</v>
+        <v>0.6121900243379701</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7071812214044162</v>
+        <v>0.7018102247861547</v>
       </c>
     </row>
     <row r="9">
@@ -6470,42 +7298,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH3-LR2e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR3e-05-WD0.1-B16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6356679047364483</v>
+        <v>0.6536875104815234</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6422787052556931</v>
+        <v>0.6539589404360659</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6309959829413968</v>
+        <v>0.6534776115381911</v>
       </c>
       <c r="L9" t="n">
-        <v>0.723095285458524</v>
+        <v>0.7380147205092501</v>
       </c>
     </row>
     <row r="10">
@@ -6516,42 +7344,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6010133140246318</v>
+        <v>0.6161844759507634</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6022243748225815</v>
+        <v>0.6261844733242263</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6001102242493958</v>
+        <v>0.6093547713635835</v>
       </c>
       <c r="L10" t="n">
-        <v>0.696240302367217</v>
+        <v>0.7071812214044162</v>
       </c>
     </row>
     <row r="11">
@@ -6562,24 +7390,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH3-LR2e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G11" t="n">
         <v>0.01</v>
@@ -6588,16 +7416,16 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6231946321440852</v>
+        <v>0.6356679047364483</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6287241517446706</v>
+        <v>0.6422787052556931</v>
       </c>
       <c r="K11" t="n">
-        <v>0.619733011029279</v>
+        <v>0.6309959829413968</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7153371792321465</v>
+        <v>0.723095285458524</v>
       </c>
     </row>
     <row r="12">
@@ -6608,7 +7436,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6618,32 +7446,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH4-LR2e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6132418348757264</v>
+        <v>0.6010133140246318</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6259099894322943</v>
+        <v>0.6022243748225815</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6063330820524419</v>
+        <v>0.6001102242493958</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7023075392878456</v>
+        <v>0.696240302367217</v>
       </c>
     </row>
     <row r="13">
@@ -6654,7 +7482,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert-base-uncased</t>
+          <t>ConfliBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6664,31 +7492,123 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bert-base-uncased-EPOCH3-LR2e-5-WD0.01-B16</t>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>3</v>
       </c>
       <c r="F13" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6231946321440852</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6287241517446706</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.619733011029279</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7153371792321465</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ElecDeb60to20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH3-LR5e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6132418348757264</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6259099894322943</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6063330820524419</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7023075392878456</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>multi_class_classification_ElecDeb60to20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bert-base-uncased-EPOCH3-LR2e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
         <v>2e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.5973218502362674</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.6009831759396437</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.5941854600135872</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.6973343942709369</v>
       </c>
     </row>
@@ -6703,7 +7623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6868,21 +7788,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased</t>
+          <t>deberta-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-cased-EPOCH2-LR2e-5-WD0.01-B16</t>
+          <t>deberta-base-EPOCH3-LR2e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>2e-05</v>
@@ -6891,19 +7811,19 @@
         <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6314496314496314</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6522842639593909</v>
+        <v>0.6043956043956044</v>
       </c>
       <c r="K4" t="n">
-        <v>0.611904761904762</v>
+        <v>0.6547619047619048</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6143958868894601</v>
+        <v>0.5822622107969152</v>
       </c>
     </row>
     <row r="5">
@@ -6914,21 +7834,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased</t>
+          <t>ConfliBERT-cont-cased</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ConfliBERT-cont-uncased-EPOCH3-LR2e-5-WD0.01-B16</t>
+          <t>ConfliBERT-cont-cased-EPOCH2-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>2e-05</v>
@@ -6940,13 +7860,13 @@
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6394230769230769</v>
+        <v>0.6314496314496314</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6456310679611651</v>
+        <v>0.6522842639593909</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.611904761904762</v>
       </c>
       <c r="L5" t="n">
         <v>0.6143958868894601</v>
@@ -6960,7 +7880,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased</t>
+          <t>ConfliBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6970,14 +7890,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B16</t>
+          <t>ConfliBERT-cont-uncased-EPOCH3-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>3e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.01</v>
@@ -6986,16 +7906,16 @@
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6711711711711712</v>
+        <v>0.6394230769230769</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6367521367521367</v>
+        <v>0.6456310679611651</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7095238095238096</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6246786632390745</v>
+        <v>0.6143958868894601</v>
       </c>
     </row>
     <row r="7">
@@ -7006,7 +7926,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ModernBERT-base</t>
+          <t>roberta-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7016,32 +7936,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B16</t>
+          <t>roberta-base-EPOCH4-LR2e-5-WD0.01-B32</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>5e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="G7" t="n">
         <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6751152073732719</v>
+        <v>0.6177884615384616</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6540178571428571</v>
+        <v>0.6237864077669902</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6976190476190476</v>
+        <v>0.611904761904762</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6375321336760925</v>
+        <v>0.5912596401028277</v>
       </c>
     </row>
     <row r="8">
@@ -7052,7 +7972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased</t>
+          <t>NEWRooseBERT-scr-uncased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7062,11 +7982,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR3e-5-WD0.01-B8</t>
+          <t>NEWRooseBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>3e-05</v>
@@ -7075,19 +7995,19 @@
         <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6477541371158393</v>
+        <v>0.6711711711711712</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6431924882629108</v>
+        <v>0.6367521367521367</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6523809523809524</v>
+        <v>0.7095238095238096</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6169665809768637</v>
+        <v>0.6246786632390745</v>
       </c>
     </row>
     <row r="9">
@@ -7098,42 +8018,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased</t>
+          <t>ModernBERT-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
+          <t>ModernBERT-base-EPOCH2-LR5e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6460396039603961</v>
+        <v>0.6751152073732719</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6726804123711341</v>
+        <v>0.6540178571428571</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6214285714285714</v>
+        <v>0.6976190476190476</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6323907455012854</v>
+        <v>0.6375321336760925</v>
       </c>
     </row>
     <row r="10">
@@ -7144,42 +8064,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>NEWRooseBERT-cont-uncased</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cased</t>
+          <t>uncased</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bert-base-cased-EPOCH3-LR2e-5-WD0.01-B16</t>
+          <t>NEWRooseBERT-cont-uncased-EPOCH2-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6090047393364929</v>
+        <v>0.6477541371158393</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6061320754716981</v>
+        <v>0.6431924882629108</v>
       </c>
       <c r="K10" t="n">
-        <v>0.611904761904762</v>
+        <v>0.6523809523809524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5758354755784062</v>
+        <v>0.6169665809768637</v>
       </c>
     </row>
     <row r="11">
@@ -7190,17 +8110,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased</t>
+          <t>NEWRooseBERT-scr-cased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uncased</t>
+          <t>cased</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
+          <t>NEWRooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B8</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7213,19 +8133,19 @@
         <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6370370370370371</v>
+        <v>0.6460396039603961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.6726804123711341</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.6214285714285714</v>
       </c>
       <c r="L11" t="n">
-        <v>0.622107969151671</v>
+        <v>0.6323907455012854</v>
       </c>
     </row>
     <row r="12">
@@ -7236,7 +8156,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased</t>
+          <t>bert-base-cased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7246,11 +8166,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+          <t>bert-base-cased-EPOCH3-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>2e-05</v>
@@ -7262,16 +8182,16 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6706021251475797</v>
+        <v>0.6090047393364929</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6651053864168618</v>
+        <v>0.6061320754716981</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6761904761904762</v>
+        <v>0.611904761904762</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6413881748071979</v>
+        <v>0.5758354755784062</v>
       </c>
     </row>
     <row r="13">
@@ -7282,41 +8202,133 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>ConfliBERT-scr-uncased</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>uncased</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ConfliBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6370370370370371</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6615384615384615</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.622107969151671</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>binary_classification_AusHansard</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cased</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NEWRooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6706021251475797</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6651053864168618</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6761904761904762</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6413881748071979</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>binary_classification_AusHansard</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>bert-base-uncased</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>uncased</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>2e-05</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>0.6463547334058759</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>0.5951903807615231</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>0.7071428571428572</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>0.5822622107969152</v>
       </c>
     </row>
